--- a/metadata/codebook-052026.xlsx
+++ b/metadata/codebook-052026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enesisik/Library/CloudStorage/Dropbox/research/data-layer/tr-silc-panel/metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enes/Library/CloudStorage/Dropbox/research/data-layer/tr-silc-panel/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF16C5E-3B2B-6C47-A995-9CBD684A40C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C529EA-D533-9B44-9C8D-28A44A3D6AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Value labels by wave" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4650" uniqueCount="768">
   <si>
     <t>Dataset</t>
   </si>
@@ -2593,9 +2593,6 @@
   </si>
   <si>
     <t>Variable name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable name </t>
   </si>
   <si>
     <r>
@@ -2856,7 +2853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2890,9 +2887,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3207,11 +3201,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:S156"/>
+  <dimension ref="A1:S153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="27.83203125" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="34.83203125" hidden="1" customWidth="1"/>
@@ -3226,10 +3221,10 @@
         <v>426</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>1</v>
@@ -3285,7 +3280,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -3344,7 +3339,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>30</v>
@@ -3403,7 +3398,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
@@ -3462,7 +3457,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>36</v>
@@ -3521,7 +3516,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>100</v>
@@ -3580,7 +3575,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>22</v>
@@ -3639,7 +3634,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
@@ -3698,7 +3693,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -3751,13 +3746,13 @@
     </row>
     <row r="10" spans="1:19" ht="210" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -3816,7 +3811,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
@@ -3875,7 +3870,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -3926,122 +3921,122 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="90" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>766</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>767</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>579</v>
+      <c r="G13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>581</v>
+        <v>460</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>583</v>
+        <v>460</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>585</v>
+        <v>460</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>587</v>
+        <v>460</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>589</v>
+        <v>460</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>591</v>
+        <v>460</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>593</v>
+        <v>460</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>595</v>
+        <v>460</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>597</v>
+        <v>460</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>599</v>
+        <v>460</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="90" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>768</v>
+        <v>42</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>40</v>
+      <c r="G14" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>464</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
@@ -4049,16 +4044,16 @@
         <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>450</v>
@@ -4067,40 +4062,40 @@
         <v>660</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>464</v>
+        <v>601</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>464</v>
+        <v>602</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>464</v>
+        <v>603</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>464</v>
+        <v>604</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>464</v>
+        <v>605</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>464</v>
+        <v>606</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>464</v>
+        <v>607</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>464</v>
+        <v>608</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>464</v>
+        <v>609</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>464</v>
+        <v>610</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>464</v>
+        <v>611</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
@@ -4108,353 +4103,353 @@
         <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>660</v>
+      <c r="G16" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>601</v>
+        <v>50</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>602</v>
+        <v>50</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>603</v>
+        <v>50</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>604</v>
+        <v>50</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>605</v>
+        <v>50</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>606</v>
+        <v>50</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>607</v>
+        <v>50</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>608</v>
+        <v>50</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>609</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>610</v>
+        <v>50</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>611</v>
+        <v>50</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="90" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>50</v>
+      <c r="G17" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>656</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>50</v>
+        <v>680</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>50</v>
+        <v>679</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>50</v>
+        <v>679</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>50</v>
+        <v>679</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="90" x14ac:dyDescent="0.2">
+        <v>679</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>656</v>
+      <c r="G18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>680</v>
+        <v>58</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>679</v>
+        <v>58</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>679</v>
+        <v>58</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>679</v>
+        <v>58</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="165" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>58</v>
+      <c r="G19" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>659</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>58</v>
+        <v>655</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="165" x14ac:dyDescent="0.2">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>659</v>
+      <c r="G20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>65</v>
+        <v>470</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R21" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -4462,46 +4457,46 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>470</v>
+        <v>576</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>470</v>
+        <v>579</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>470</v>
+        <v>581</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>470</v>
+        <v>583</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>470</v>
+        <v>585</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>470</v>
+        <v>587</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>470</v>
+        <v>589</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>470</v>
+        <v>591</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>470</v>
+        <v>593</v>
       </c>
       <c r="P22" s="11" t="s">
         <v>660</v>
@@ -4516,51 +4511,51 @@
         <v>660</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>576</v>
+        <v>471</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>579</v>
+        <v>471</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>581</v>
+        <v>471</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>583</v>
+        <v>471</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>585</v>
+        <v>471</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>587</v>
+        <v>471</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>589</v>
+        <v>471</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>591</v>
+        <v>471</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>593</v>
+        <v>471</v>
       </c>
       <c r="P23" s="11" t="s">
         <v>660</v>
@@ -4575,51 +4570,51 @@
         <v>660</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>471</v>
+      <c r="G24" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>675</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>471</v>
+        <v>661</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>471</v>
+        <v>661</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>471</v>
+        <v>661</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>471</v>
+        <v>661</v>
       </c>
       <c r="P24" s="11" t="s">
         <v>660</v>
@@ -4634,63 +4629,63 @@
         <v>660</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>675</v>
+      <c r="G25" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="P25" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q25" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R25" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S25" s="11" t="s">
-        <v>660</v>
+        <v>662</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -4698,176 +4693,176 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>662</v>
+        <v>612</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>667</v>
+      <c r="G27" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>676</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>612</v>
+        <v>677</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>676</v>
+      <c r="G28" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>479</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>677</v>
+        <v>479</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>677</v>
+        <v>479</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>677</v>
+        <v>479</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>677</v>
+        <v>479</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>677</v>
+        <v>479</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>678</v>
+        <v>479</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>677</v>
+        <v>479</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>677</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
@@ -4875,58 +4870,58 @@
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -4934,143 +4929,143 @@
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>481</v>
+      <c r="G31" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R31" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S31" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="G32" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" s="11" t="s">
         <v>660</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>660</v>
@@ -5106,63 +5101,63 @@
         <v>660</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" ht="225" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>485</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>587</v>
+        <v>613</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>613</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>589</v>
+        <v>486</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>591</v>
+        <v>486</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>593</v>
+        <v>486</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>595</v>
+        <v>486</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>597</v>
+        <v>486</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>599</v>
+        <v>486</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>443</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5170,117 +5165,117 @@
         <v>102</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>105</v>
+        <v>682</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R34" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S34" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="225" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>109</v>
+        <v>683</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>613</v>
+        <v>489</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>614</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>490</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5288,16 +5283,16 @@
         <v>102</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>489</v>
@@ -5342,63 +5337,63 @@
         <v>490</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>614</v>
+      <c r="G37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>490</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5406,176 +5401,176 @@
         <v>102</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>614</v>
+      <c r="G38" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>493</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>493</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5583,134 +5578,134 @@
         <v>102</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>489</v>
@@ -5755,21 +5750,21 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>489</v>
@@ -5814,80 +5809,80 @@
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K45" s="3" t="s">
+      <c r="G45" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="K45" s="8" t="s">
         <v>130</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>489</v>
@@ -5907,29 +5902,29 @@
       <c r="K46" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>130</v>
+      <c r="L46" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O46" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P46" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q46" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R46" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S46" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5937,58 +5932,58 @@
         <v>102</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>130</v>
+        <v>500</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5996,58 +5991,58 @@
         <v>102</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>130</v>
+        <v>502</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>130</v>
+        <v>502</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>130</v>
+        <v>502</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>130</v>
+        <v>502</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L48" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M48" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N48" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O48" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P48" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q48" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R48" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S48" s="11" t="s">
-        <v>660</v>
+        <v>502</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -6055,16 +6050,16 @@
         <v>102</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>500</v>
@@ -6109,21 +6104,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>500</v>
@@ -6173,16 +6168,16 @@
         <v>102</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>500</v>
@@ -6227,21 +6222,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>500</v>
@@ -6291,16 +6286,16 @@
         <v>102</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>500</v>
@@ -6350,16 +6345,16 @@
         <v>102</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>500</v>
@@ -6409,16 +6404,16 @@
         <v>102</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>500</v>
@@ -6467,17 +6462,17 @@
       <c r="A56" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>155</v>
+      <c r="B56" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>500</v>
@@ -6491,64 +6486,62 @@
       <c r="I56" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+      <c r="J56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R56" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S56" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>157</v>
-      </c>
+      <c r="B57" s="13"/>
       <c r="C57" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>502</v>
+      <c r="G57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>502</v>
@@ -6581,21 +6574,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="13" t="s">
-        <v>159</v>
+      <c r="B58" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>500</v>
@@ -6609,62 +6602,64 @@
       <c r="I58" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="J58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R58" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S58" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="J58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B59" s="14"/>
+      <c r="B59" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="C59" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G59" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>660</v>
+      <c r="G59" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>502</v>
@@ -6697,63 +6692,63 @@
         <v>502</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>500</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -6761,16 +6756,16 @@
         <v>102</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>500</v>
@@ -6820,75 +6815,75 @@
         <v>102</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>500</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>169</v>
+      <c r="B63" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>500</v>
@@ -6902,11 +6897,11 @@
       <c r="I63" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>502</v>
+      <c r="J63" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>502</v>
@@ -6933,33 +6928,31 @@
         <v>502</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>171</v>
-      </c>
+      <c r="B64" s="13"/>
       <c r="C64" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>502</v>
+      <c r="G64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>502</v>
@@ -6967,46 +6960,46 @@
       <c r="K64" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="L64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="L64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R64" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S64" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B65" s="13" t="s">
-        <v>173</v>
+      <c r="B65" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>500</v>
@@ -7020,11 +7013,11 @@
       <c r="I65" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="J65" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K65" s="11" t="s">
-        <v>660</v>
+      <c r="J65" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>502</v>
@@ -7055,21 +7048,23 @@
       <c r="A66" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B66" s="14"/>
+      <c r="B66" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="C66" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G66" s="11" t="s">
-        <v>660</v>
+      <c r="G66" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="H66" s="11" t="s">
         <v>660</v>
@@ -7077,11 +7072,11 @@
       <c r="I66" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>502</v>
+      <c r="J66" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="L66" s="11" t="s">
         <v>660</v>
@@ -7113,16 +7108,16 @@
         <v>102</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>500</v>
@@ -7172,16 +7167,16 @@
         <v>102</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>500</v>
@@ -7189,41 +7184,41 @@
       <c r="G68" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R68" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S68" s="11" t="s">
-        <v>660</v>
+      <c r="H68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="R68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -7231,16 +7226,16 @@
         <v>102</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>500</v>
@@ -7251,55 +7246,55 @@
       <c r="H69" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R69" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="I69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R69" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S69" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>500</v>
@@ -7310,392 +7305,392 @@
       <c r="H70" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R70" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+      <c r="I70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R70" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S70" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R71" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S71" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>512</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="R71" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>502</v>
+        <v>193</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R72" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S72" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>512</v>
+        <v>615</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>512</v>
+        <v>615</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>512</v>
+        <v>616</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>512</v>
+        <v>617</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>512</v>
+        <v>618</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>512</v>
+        <v>619</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>512</v>
+        <v>620</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>512</v>
+        <v>621</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>512</v>
+        <v>622</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>512</v>
+        <v>623</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>512</v>
+        <v>624</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>512</v>
+        <v>625</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>193</v>
+      <c r="G74" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>615</v>
+        <v>516</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>615</v>
+        <v>516</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>616</v>
+        <v>516</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>617</v>
+        <v>516</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>618</v>
+        <v>516</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>619</v>
+        <v>516</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>620</v>
+        <v>516</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>621</v>
+        <v>516</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>622</v>
+        <v>516</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>623</v>
+        <v>516</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>624</v>
+        <v>516</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>625</v>
+        <v>516</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H76" s="11" t="s">
-        <v>660</v>
+      <c r="G76" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>516</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.2">
@@ -7703,412 +7698,412 @@
         <v>102</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>202</v>
+      <c r="G78" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>626</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="Q79" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="R79" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="S79" s="3" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+      <c r="P79" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q79" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R79" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S79" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>626</v>
+        <v>130</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>207</v>
+        <v>130</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="S80" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>210</v>
+      <c r="G81" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P81" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q81" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R81" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S81" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G82" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J82" s="8" t="s">
+      <c r="G82" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>130</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="S82" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J83" s="8" t="s">
+      <c r="G83" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J83" s="3" t="s">
         <v>130</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.2">
@@ -8116,16 +8111,16 @@
         <v>102</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>511</v>
@@ -8170,122 +8165,122 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="S85" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="S86" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -8293,16 +8288,16 @@
         <v>102</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>511</v>
@@ -8352,16 +8347,16 @@
         <v>102</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>511</v>
@@ -8411,16 +8406,16 @@
         <v>102</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>511</v>
@@ -8470,16 +8465,16 @@
         <v>102</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>511</v>
@@ -8529,16 +8524,16 @@
         <v>102</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>511</v>
@@ -8588,16 +8583,16 @@
         <v>102</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>511</v>
@@ -8647,16 +8642,16 @@
         <v>102</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>511</v>
@@ -8706,16 +8701,16 @@
         <v>102</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>511</v>
@@ -8765,58 +8760,58 @@
         <v>102</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -8824,143 +8819,143 @@
         <v>102</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>102</v>
+        <v>249</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>743</v>
+        <v>252</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>130</v>
+        <v>522</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>102</v>
+        <v>249</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>744</v>
+        <v>256</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>130</v>
+        <v>522</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>628</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>130</v>
@@ -8996,63 +8991,63 @@
         <v>130</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" ht="75" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>576</v>
+        <v>261</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>579</v>
+        <v>261</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>581</v>
+        <v>261</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>583</v>
+        <v>261</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>585</v>
+        <v>261</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>587</v>
+        <v>261</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>589</v>
+        <v>261</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>591</v>
+        <v>261</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>593</v>
+        <v>261</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>595</v>
+        <v>261</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>597</v>
+        <v>261</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>599</v>
+        <v>261</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>443</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9060,176 +9055,176 @@
         <v>249</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="I100" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>254</v>
+        <v>526</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>506</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="H101" s="8" t="s">
-        <v>628</v>
+        <v>526</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>506</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>130</v>
+        <v>529</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="Q101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>130</v>
+        <v>506</v>
       </c>
       <c r="S101" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19" ht="75" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>261</v>
+        <v>526</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>506</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>261</v>
+        <v>527</v>
       </c>
     </row>
     <row r="103" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9237,16 +9232,16 @@
         <v>249</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>526</v>
@@ -9257,7 +9252,7 @@
       <c r="H103" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="I103" s="3" t="s">
+      <c r="I103" s="4" t="s">
         <v>529</v>
       </c>
       <c r="J103" s="3" t="s">
@@ -9296,27 +9291,27 @@
         <v>249</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>526</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>629</v>
+        <v>506</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="I104" s="3" t="s">
+      <c r="I104" s="4" t="s">
         <v>529</v>
       </c>
       <c r="J104" s="3" t="s">
@@ -9350,80 +9345,80 @@
         <v>506</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="G105" s="8" t="s">
+      <c r="G105" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="H105" s="8" t="s">
+      <c r="H105" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="I105" s="3" t="s">
-        <v>527</v>
+      <c r="I105" s="4" t="s">
+        <v>529</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="P105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="Q105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="S105" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>526</v>
@@ -9473,16 +9468,16 @@
         <v>249</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>526</v>
@@ -9532,16 +9527,16 @@
         <v>249</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>526</v>
@@ -9586,21 +9581,21 @@
         <v>506</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>526</v>
@@ -9650,16 +9645,16 @@
         <v>249</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>526</v>
@@ -9709,16 +9704,16 @@
         <v>249</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>526</v>
@@ -9732,35 +9727,35 @@
       <c r="I111" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="J111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="K111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="M111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="O111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="P111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="R111" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="S111" s="3" t="s">
-        <v>506</v>
+      <c r="J111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R111" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S111" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="112" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9768,16 +9763,16 @@
         <v>249</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>526</v>
@@ -9791,7 +9786,7 @@
       <c r="I112" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="J112" s="3" t="s">
+      <c r="J112" s="4" t="s">
         <v>506</v>
       </c>
       <c r="K112" s="3" t="s">
@@ -9827,117 +9822,117 @@
         <v>249</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="G113" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="H113" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="I113" s="4" t="s">
-        <v>529</v>
+      <c r="I113" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="P113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="Q113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="R113" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="S113" s="3" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" ht="150" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="I114" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R114" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S114" s="11" t="s">
-        <v>660</v>
+        <v>531</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="N114" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="P114" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="Q114" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="R114" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="S114" s="3" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="115" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9945,58 +9940,58 @@
         <v>249</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="I115" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="J115" s="4" t="s">
-        <v>506</v>
+        <v>130</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="N115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="Q115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="R115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="S115" s="3" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -10004,117 +9999,117 @@
         <v>249</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>506</v>
+        <v>531</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="N116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="P116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="Q116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="R116" s="3" t="s">
-        <v>527</v>
+        <v>130</v>
       </c>
       <c r="S116" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" ht="150" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="G117" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="H117" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="I117" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="J117" s="8" t="s">
-        <v>630</v>
+      <c r="G117" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>749</v>
+        <v>130</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>749</v>
+        <v>130</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>750</v>
+        <v>130</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>750</v>
+        <v>130</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>750</v>
+        <v>130</v>
       </c>
       <c r="P117" s="3" t="s">
-        <v>750</v>
+        <v>130</v>
       </c>
       <c r="Q117" s="3" t="s">
-        <v>750</v>
+        <v>130</v>
       </c>
       <c r="R117" s="3" t="s">
-        <v>750</v>
+        <v>130</v>
       </c>
       <c r="S117" s="3" t="s">
-        <v>750</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -10122,16 +10117,16 @@
         <v>249</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>531</v>
@@ -10176,299 +10171,299 @@
         <v>130</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="R119" s="3" t="s">
-        <v>130</v>
+        <v>322</v>
       </c>
       <c r="S119" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" ht="135" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J120" s="3" t="s">
-        <v>130</v>
+        <v>535</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="J120" s="8" t="s">
+        <v>750</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="P120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="Q120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="R120" s="3" t="s">
-        <v>130</v>
+        <v>751</v>
       </c>
       <c r="S120" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>130</v>
+        <v>535</v>
+      </c>
+      <c r="G121" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>130</v>
+        <v>631</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>130</v>
+        <v>539</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>130</v>
+        <v>539</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>130</v>
+        <v>539</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>130</v>
+        <v>539</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>130</v>
+        <v>539</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>130</v>
+        <v>539</v>
       </c>
       <c r="P121" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q121" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="R121" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="S121" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>539</v>
+      </c>
+      <c r="Q121" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R121" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S121" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>535</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="P122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="Q122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="R122" s="3" t="s">
-        <v>322</v>
+        <v>541</v>
       </c>
       <c r="S122" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="123" spans="1:19" ht="135" x14ac:dyDescent="0.2">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>535</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>751</v>
+        <v>516</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="I123" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="J123" s="8" t="s">
-        <v>751</v>
+        <v>516</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="P123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="Q123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="R123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
       <c r="S123" s="3" t="s">
-        <v>752</v>
+        <v>527</v>
       </c>
     </row>
     <row r="124" spans="1:19" ht="60" x14ac:dyDescent="0.2">
@@ -10476,528 +10471,528 @@
         <v>249</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="G124" s="11" t="s">
-        <v>660</v>
+        <v>543</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="I124" s="4" t="s">
-        <v>632</v>
+        <v>322</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>539</v>
+        <v>322</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>539</v>
+        <v>322</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>539</v>
+        <v>322</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>539</v>
+        <v>322</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>539</v>
+        <v>322</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>539</v>
+        <v>322</v>
       </c>
       <c r="P124" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="Q124" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R124" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S124" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+      <c r="Q124" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="R124" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="S124" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" ht="135" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="I125" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="J125" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="J125" s="8" t="s">
+        <v>750</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="P125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="Q125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="R125" s="3" t="s">
-        <v>541</v>
+        <v>751</v>
       </c>
       <c r="S125" s="3" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>516</v>
+        <v>633</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="I126" s="3" t="s">
-        <v>527</v>
+        <v>633</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>634</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>527</v>
+        <v>635</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>527</v>
+        <v>635</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="P126" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="R126" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="S126" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>335</v>
+        <v>755</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>336</v>
+        <v>756</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="I127" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="J127" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="K127" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="L127" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="M127" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="N127" s="3" t="s">
-        <v>322</v>
+        <v>757</v>
+      </c>
+      <c r="F127" s="2"/>
+      <c r="G127" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I127" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J127" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K127" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L127" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M127" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N127" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>322</v>
+        <v>758</v>
       </c>
       <c r="P127" s="3" t="s">
-        <v>322</v>
+        <v>759</v>
       </c>
       <c r="Q127" s="3" t="s">
-        <v>322</v>
+        <v>760</v>
       </c>
       <c r="R127" s="3" t="s">
-        <v>322</v>
+        <v>761</v>
       </c>
       <c r="S127" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="128" spans="1:19" ht="135" x14ac:dyDescent="0.2">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="H128" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="I128" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="J128" s="8" t="s">
-        <v>751</v>
+        <v>548</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>549</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="N128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="P128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="Q128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="R128" s="3" t="s">
-        <v>752</v>
+        <v>549</v>
       </c>
       <c r="S128" s="3" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="J129" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="K129" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
+      </c>
+      <c r="J129" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K129" s="4" t="s">
+        <v>550</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="O129" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="P129" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="Q129" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="R129" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="S129" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
+        <v>550</v>
+      </c>
+      <c r="O129" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P129" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q129" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R129" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S129" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>756</v>
+        <v>350</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>757</v>
+        <v>351</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="F130" s="2"/>
-      <c r="G130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N130" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O130" s="12" t="s">
-        <v>759</v>
-      </c>
-      <c r="P130" s="12" t="s">
-        <v>760</v>
-      </c>
-      <c r="Q130" s="12" t="s">
-        <v>761</v>
-      </c>
-      <c r="R130" s="12" t="s">
-        <v>762</v>
-      </c>
-      <c r="S130" s="12" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="K130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="M130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="N130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="O130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="P130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="R130" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="S130" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G131" s="3" t="s">
-        <v>549</v>
+      <c r="G131" s="8" t="s">
+        <v>632</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="I131" s="3" t="s">
-        <v>549</v>
+        <v>631</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="P131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="Q131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="R131" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="S131" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G132" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="H132" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="I132" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="J132" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="K132" s="4" t="s">
-        <v>550</v>
+      <c r="G132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>754</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>550</v>
+        <v>754</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>550</v>
+        <v>754</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="O132" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P132" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q132" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R132" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S132" s="11" t="s">
-        <v>660</v>
+        <v>754</v>
+      </c>
+      <c r="O132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="P132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="R132" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="S132" s="3" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="133" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -11005,471 +11000,471 @@
         <v>249</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G133" s="3" t="s">
-        <v>353</v>
+      <c r="G133" s="8" t="s">
+        <v>639</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="P133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="Q133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="R133" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="S133" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="134" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G134" s="8" t="s">
-        <v>632</v>
+      <c r="G134" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="I134" s="4" t="s">
-        <v>632</v>
+        <v>130</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="P134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="Q134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="R134" s="3" t="s">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="S134" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="135" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" ht="90" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>548</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="N135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="P135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="Q135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="R135" s="3" t="s">
-        <v>755</v>
+        <v>369</v>
       </c>
       <c r="S135" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="136" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>639</v>
+        <v>555</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>556</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>754</v>
+        <v>556</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>754</v>
+        <v>556</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>754</v>
+        <v>556</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>754</v>
+        <v>556</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>754</v>
+        <v>556</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>754</v>
+        <v>556</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>754</v>
+        <v>556</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="P136" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="Q136" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="R136" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="S136" s="3" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
+        <v>556</v>
+      </c>
+      <c r="P136" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q136" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R136" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S136" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="N137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="P137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="Q137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="R137" s="3" t="s">
-        <v>130</v>
+        <v>557</v>
       </c>
       <c r="S137" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19" ht="90" x14ac:dyDescent="0.2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" ht="150" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="I138" s="3" t="s">
-        <v>369</v>
+        <v>555</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="H138" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>640</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>369</v>
+        <v>641</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>369</v>
+        <v>642</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>369</v>
+        <v>643</v>
       </c>
       <c r="M138" s="3" t="s">
-        <v>369</v>
+        <v>558</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>369</v>
+        <v>558</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>369</v>
+        <v>558</v>
       </c>
       <c r="P138" s="3" t="s">
-        <v>369</v>
+        <v>558</v>
       </c>
       <c r="Q138" s="3" t="s">
-        <v>369</v>
+        <v>558</v>
       </c>
       <c r="R138" s="3" t="s">
-        <v>369</v>
+        <v>558</v>
       </c>
       <c r="S138" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" ht="150" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="G139" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="H139" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="I139" s="3" t="s">
-        <v>556</v>
+      <c r="G139" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>640</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>556</v>
+        <v>640</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>556</v>
+        <v>642</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>556</v>
+        <v>643</v>
       </c>
       <c r="M139" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N139" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O139" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="P139" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q139" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R139" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S139" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="140" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>558</v>
+      </c>
+      <c r="P139" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q139" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="R139" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="S139" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" ht="150" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="G140" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="H140" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="I140" s="3" t="s">
-        <v>557</v>
+      <c r="G140" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>640</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>557</v>
+        <v>646</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>557</v>
+        <v>642</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>557</v>
+        <v>643</v>
       </c>
       <c r="M140" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N140" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O140" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P140" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Q140" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="R140" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S140" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="141" spans="1:19" ht="150" x14ac:dyDescent="0.2">
@@ -11477,22 +11472,22 @@
         <v>249</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="H141" s="8" t="s">
         <v>640</v>
@@ -11501,7 +11496,7 @@
         <v>640</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="K141" s="3" t="s">
         <v>642</v>
@@ -11536,22 +11531,22 @@
         <v>249</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>640</v>
@@ -11560,7 +11555,7 @@
         <v>640</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="K142" s="3" t="s">
         <v>642</v>
@@ -11595,16 +11590,16 @@
         <v>249</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>555</v>
@@ -11613,7 +11608,7 @@
         <v>640</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="I143" s="8" t="s">
         <v>640</v>
@@ -11654,22 +11649,22 @@
         <v>249</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="H144" s="8" t="s">
         <v>640</v>
@@ -11713,22 +11708,22 @@
         <v>249</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>640</v>
@@ -11772,16 +11767,16 @@
         <v>249</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>555</v>
@@ -11831,16 +11826,16 @@
         <v>249</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>555</v>
@@ -11849,7 +11844,7 @@
         <v>640</v>
       </c>
       <c r="H147" s="8" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="I147" s="8" t="s">
         <v>640</v>
@@ -11890,16 +11885,16 @@
         <v>249</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>555</v>
@@ -11949,16 +11944,16 @@
         <v>249</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>555</v>
@@ -12003,181 +11998,181 @@
         <v>558</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="150" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="H150" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="I150" s="8" t="s">
-        <v>640</v>
+        <v>567</v>
+      </c>
+      <c r="G150" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H150" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I150" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>646</v>
+        <v>224</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>642</v>
+        <v>224</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>643</v>
+        <v>224</v>
       </c>
       <c r="M150" s="3" t="s">
-        <v>558</v>
+        <v>224</v>
       </c>
       <c r="N150" s="3" t="s">
-        <v>558</v>
+        <v>224</v>
       </c>
       <c r="O150" s="3" t="s">
-        <v>558</v>
+        <v>224</v>
       </c>
       <c r="P150" s="3" t="s">
-        <v>558</v>
+        <v>224</v>
       </c>
       <c r="Q150" s="3" t="s">
-        <v>558</v>
+        <v>224</v>
       </c>
       <c r="R150" s="3" t="s">
-        <v>558</v>
+        <v>224</v>
       </c>
       <c r="S150" s="3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="151" spans="1:19" ht="150" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>646</v>
+        <v>418</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>642</v>
+        <v>418</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>643</v>
+        <v>418</v>
       </c>
       <c r="M151" s="3" t="s">
-        <v>558</v>
+        <v>418</v>
       </c>
       <c r="N151" s="3" t="s">
-        <v>558</v>
+        <v>418</v>
       </c>
       <c r="O151" s="3" t="s">
-        <v>558</v>
+        <v>418</v>
       </c>
       <c r="P151" s="3" t="s">
-        <v>558</v>
+        <v>418</v>
       </c>
       <c r="Q151" s="3" t="s">
-        <v>558</v>
+        <v>418</v>
       </c>
       <c r="R151" s="3" t="s">
-        <v>558</v>
+        <v>418</v>
       </c>
       <c r="S151" s="3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="152" spans="1:19" ht="150" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="H152" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="I152" s="8" t="s">
-        <v>640</v>
+        <v>568</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>646</v>
+        <v>130</v>
       </c>
       <c r="K152" s="3" t="s">
-        <v>642</v>
+        <v>130</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>643</v>
+        <v>130</v>
       </c>
       <c r="M152" s="3" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="N152" s="3" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="P152" s="3" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="Q152" s="3" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="R152" s="3" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
       <c r="S152" s="3" t="s">
-        <v>558</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -12185,242 +12180,65 @@
         <v>249</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="G153" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H153" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I153" s="11" t="s">
-        <v>660</v>
+        <v>568</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="M153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="N153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="O153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="P153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="Q153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="R153" s="3" t="s">
-        <v>224</v>
+        <v>425</v>
       </c>
       <c r="S153" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="154" spans="1:19" ht="30" x14ac:dyDescent="0.2">
-      <c r="A154" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="H154" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="I154" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="J154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="K154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="L154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="M154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="N154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="O154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="P154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="R154" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="S154" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="155" spans="1:19" ht="30" x14ac:dyDescent="0.2">
-      <c r="A155" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="M155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="N155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="O155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="P155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="R155" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="S155" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="156" spans="1:19" ht="30" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="I156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="J156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="K156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="L156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="M156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="N156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="O156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="P156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="R156" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="S156" s="3" t="s">
         <v>425</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <mergeCells count="2">
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B63:B64"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12873,7 +12691,7 @@
         <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>39</v>
@@ -17017,7 +16835,7 @@
         <v>546</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="J131" s="3" t="s">
         <v>547</v>

--- a/metadata/codebook-052026.xlsx
+++ b/metadata/codebook-052026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enes/Library/CloudStorage/Dropbox/research/data-layer/tr-silc-panel/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C529EA-D533-9B44-9C8D-28A44A3D6AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DA6FBF-D918-A24A-9C9F-6A3D34D15982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4650" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4654" uniqueCount="768">
   <si>
     <t>Dataset</t>
   </si>
@@ -2853,7 +2853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2893,6 +2893,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3201,7 +3204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:S153"/>
+  <dimension ref="A1:S154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3272,122 +3275,92 @@
         <v>578</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>763</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>660</v>
-      </c>
+      <c r="D2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>455</v>
+      <c r="I3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -3395,16 +3368,16 @@
         <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>434</v>
@@ -3454,16 +3427,16 @@
         <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>434</v>
@@ -3513,75 +3486,75 @@
         <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>6</v>
+      <c r="G6" s="10" t="s">
+        <v>660</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>434</v>
@@ -3626,417 +3599,417 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>434</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>577</v>
+        <v>6</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>580</v>
+        <v>6</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>582</v>
+        <v>6</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>584</v>
+        <v>6</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>586</v>
+        <v>6</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>588</v>
+        <v>6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>590</v>
+        <v>6</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>592</v>
+        <v>6</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>594</v>
+        <v>6</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>596</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>598</v>
+        <v>6</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="210" x14ac:dyDescent="0.2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>250</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>658</v>
+      <c r="G10" s="3" t="s">
+        <v>576</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>445</v>
+        <v>579</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>445</v>
+        <v>581</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>445</v>
+        <v>585</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>445</v>
+        <v>587</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>445</v>
+        <v>589</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>445</v>
+        <v>591</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>445</v>
+        <v>593</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>445</v>
+        <v>595</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>445</v>
+        <v>597</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>445</v>
+        <v>599</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="75" x14ac:dyDescent="0.2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="210" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>16</v>
+      <c r="G11" s="8" t="s">
+        <v>658</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>16</v>
+        <v>445</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="120" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="75" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="120" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="N13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="O13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="Q13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="R13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="S13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="90" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>767</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>464</v>
+      <c r="G14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
@@ -4044,16 +4017,16 @@
         <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>450</v>
@@ -4062,40 +4035,40 @@
         <v>660</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>601</v>
+        <v>464</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>602</v>
+        <v>464</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>603</v>
+        <v>464</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>604</v>
+        <v>464</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>605</v>
+        <v>464</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>606</v>
+        <v>464</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>607</v>
+        <v>464</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>608</v>
+        <v>464</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>609</v>
+        <v>464</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>610</v>
+        <v>464</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>611</v>
+        <v>464</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
@@ -4103,353 +4076,353 @@
         <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>50</v>
+      <c r="G16" s="10" t="s">
+        <v>660</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>50</v>
+        <v>601</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>50</v>
+        <v>602</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>50</v>
+        <v>603</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>50</v>
+        <v>604</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>50</v>
+        <v>605</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>50</v>
+        <v>606</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>50</v>
+        <v>607</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>50</v>
+        <v>608</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>50</v>
+        <v>609</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>50</v>
+        <v>610</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>50</v>
+        <v>611</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="90" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>656</v>
+      <c r="G17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>680</v>
+        <v>50</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>679</v>
+        <v>50</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>679</v>
+        <v>50</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>679</v>
+        <v>50</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>58</v>
+      <c r="G18" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>656</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>58</v>
+        <v>680</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>58</v>
+        <v>679</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>58</v>
+        <v>679</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>58</v>
+        <v>679</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="165" x14ac:dyDescent="0.2">
+        <v>679</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>659</v>
+      <c r="G19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>655</v>
+        <v>58</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="165" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>65</v>
+      <c r="G20" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>659</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>65</v>
+        <v>655</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="P21" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q21" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R21" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S21" s="11" t="s">
-        <v>660</v>
+        <v>65</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -4457,46 +4430,46 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>576</v>
+        <v>470</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>579</v>
+        <v>470</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>581</v>
+        <v>470</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>583</v>
+        <v>470</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>585</v>
+        <v>470</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>587</v>
+        <v>470</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>589</v>
+        <v>470</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>591</v>
+        <v>470</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>593</v>
+        <v>470</v>
       </c>
       <c r="P22" s="11" t="s">
         <v>660</v>
@@ -4511,51 +4484,51 @@
         <v>660</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>471</v>
+        <v>576</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>471</v>
+        <v>579</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>471</v>
+        <v>581</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>471</v>
+        <v>583</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>471</v>
+        <v>585</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>471</v>
+        <v>587</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>471</v>
+        <v>589</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>471</v>
+        <v>591</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>471</v>
+        <v>593</v>
       </c>
       <c r="P23" s="11" t="s">
         <v>660</v>
@@ -4570,51 +4543,51 @@
         <v>660</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>675</v>
+      <c r="G24" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>471</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>661</v>
+        <v>471</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>661</v>
+        <v>471</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>661</v>
+        <v>471</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>661</v>
+        <v>471</v>
       </c>
       <c r="P24" s="11" t="s">
         <v>660</v>
@@ -4629,63 +4602,63 @@
         <v>660</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>662</v>
+      <c r="G25" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>675</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R25" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -4693,176 +4666,176 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>612</v>
+        <v>662</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>676</v>
+      <c r="G27" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>479</v>
+      <c r="G28" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>676</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>479</v>
+        <v>678</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>479</v>
+        <v>677</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>479</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
@@ -4870,58 +4843,58 @@
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -4929,143 +4902,143 @@
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>450</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G31" s="11" t="s">
-        <v>660</v>
+      <c r="G31" s="3" t="s">
+        <v>481</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R31" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S31" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>481</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H32" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>660</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>484</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>660</v>
@@ -5101,122 +5074,122 @@
         <v>660</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="225" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>485</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R33" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="225" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>682</v>
+        <v>109</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>614</v>
+        <v>485</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>613</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>490</v>
+        <v>613</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>613</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5224,16 +5197,16 @@
         <v>102</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>489</v>
@@ -5283,16 +5256,16 @@
         <v>102</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>489</v>
@@ -5337,122 +5310,122 @@
         <v>490</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>119</v>
+      <c r="G37" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>614</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>119</v>
+        <v>490</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>493</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5460,176 +5433,176 @@
         <v>102</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>124</v>
+        <v>493</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>489</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5637,16 +5610,16 @@
         <v>102</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>489</v>
@@ -5691,21 +5664,21 @@
         <v>130</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>489</v>
@@ -5755,16 +5728,16 @@
         <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>489</v>
@@ -5809,63 +5782,63 @@
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G45" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="K45" s="8" t="s">
+      <c r="G45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>130</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5873,58 +5846,58 @@
         <v>102</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L46" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N46" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O46" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P46" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q46" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R46" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S46" s="11" t="s">
-        <v>660</v>
+      <c r="G46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5932,58 +5905,58 @@
         <v>102</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>502</v>
+        <v>130</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>502</v>
+        <v>130</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>502</v>
+        <v>130</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>502</v>
+        <v>130</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>502</v>
+        <v>130</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N47" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O47" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P47" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q47" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R47" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5991,16 +5964,16 @@
         <v>102</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>500</v>
@@ -6050,16 +6023,16 @@
         <v>102</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>500</v>
@@ -6104,21 +6077,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>500</v>
@@ -6163,21 +6136,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>500</v>
@@ -6227,16 +6200,16 @@
         <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>500</v>
@@ -6286,16 +6259,16 @@
         <v>102</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>500</v>
@@ -6345,16 +6318,16 @@
         <v>102</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>500</v>
@@ -6404,16 +6377,16 @@
         <v>102</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>500</v>
@@ -6462,17 +6435,17 @@
       <c r="A56" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>159</v>
+      <c r="B56" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>500</v>
@@ -6486,121 +6459,121 @@
       <c r="I56" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="J56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R56" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S56" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="J56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B57" s="13"/>
+      <c r="B57" s="12" t="s">
+        <v>159</v>
+      </c>
       <c r="C57" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="G57" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J57" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="K57" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="L57" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>502</v>
+      <c r="M57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R57" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S57" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="B58" s="13"/>
       <c r="C58" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>502</v>
+      <c r="G58" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>502</v>
@@ -6633,21 +6606,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>500</v>
@@ -6697,58 +6670,58 @@
         <v>102</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>500</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -6756,58 +6729,58 @@
         <v>102</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>500</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -6815,16 +6788,16 @@
         <v>102</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>500</v>
@@ -6869,21 +6842,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B63" s="12" t="s">
-        <v>173</v>
+      <c r="B63" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>500</v>
@@ -6897,11 +6870,11 @@
       <c r="I63" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="J63" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K63" s="11" t="s">
-        <v>660</v>
+      <c r="J63" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>502</v>
@@ -6932,86 +6905,86 @@
       <c r="A64" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B64" s="13"/>
+      <c r="B64" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="C64" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J64" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="K64" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="I64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R64" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S64" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+      <c r="L64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="B65" s="13"/>
       <c r="C65" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>502</v>
+      <c r="G65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>502</v>
@@ -7019,46 +6992,46 @@
       <c r="K65" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="L65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R65" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S65" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="L65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R65" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S65" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>500</v>
@@ -7066,58 +7039,58 @@
       <c r="G66" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R66" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S66" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+      <c r="H66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>500</v>
@@ -7125,58 +7098,58 @@
       <c r="G67" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="R67" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S67" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="H67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R67" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S67" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>500</v>
@@ -7221,21 +7194,21 @@
         <v>502</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>500</v>
@@ -7246,38 +7219,38 @@
       <c r="H69" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R69" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S69" s="11" t="s">
-        <v>660</v>
+      <c r="I69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="R69" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -7285,16 +7258,16 @@
         <v>102</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>500</v>
@@ -7339,240 +7312,240 @@
         <v>660</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="R71" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R71" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S71" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>193</v>
+        <v>512</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>615</v>
+        <v>193</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>615</v>
+        <v>193</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>616</v>
+        <v>193</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>617</v>
+        <v>193</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>618</v>
+        <v>193</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>619</v>
+        <v>193</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>620</v>
+        <v>193</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>621</v>
+        <v>193</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>622</v>
+        <v>193</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>623</v>
+        <v>193</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>624</v>
+        <v>193</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>625</v>
+        <v>193</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G74" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H74" s="11" t="s">
-        <v>660</v>
+      <c r="G74" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>615</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>516</v>
+        <v>616</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>516</v>
+        <v>618</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>516</v>
+        <v>619</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>516</v>
+        <v>620</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>516</v>
+        <v>621</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>516</v>
+        <v>622</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>516</v>
+        <v>623</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>516</v>
+        <v>624</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>516</v>
+        <v>625</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.2">
@@ -7580,25 +7553,25 @@
         <v>102</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>516</v>
+      <c r="G75" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>516</v>
@@ -7634,299 +7607,299 @@
         <v>516</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>202</v>
+        <v>516</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>518</v>
+        <v>202</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G78" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>626</v>
+      <c r="G78" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>518</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>210</v>
+      <c r="G79" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>626</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P79" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q79" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R79" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S79" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q79" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="R79" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="S79" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G80" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J80" s="8" t="s">
-        <v>130</v>
+      <c r="G80" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="P80" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q80" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="R80" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="S80" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
+      </c>
+      <c r="P80" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q80" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R80" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S80" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -7934,16 +7907,16 @@
         <v>102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>511</v>
@@ -7988,63 +7961,63 @@
         <v>213</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J82" s="3" t="s">
+      <c r="G82" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J82" s="8" t="s">
         <v>130</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="S82" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.2">
@@ -8052,16 +8025,16 @@
         <v>102</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>511</v>
@@ -8111,16 +8084,16 @@
         <v>102</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>511</v>
@@ -8165,63 +8138,63 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>511</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="S85" s="3" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -8229,16 +8202,16 @@
         <v>102</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>511</v>
@@ -8288,16 +8261,16 @@
         <v>102</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>511</v>
@@ -8347,16 +8320,16 @@
         <v>102</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>511</v>
@@ -8406,16 +8379,16 @@
         <v>102</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>511</v>
@@ -8465,16 +8438,16 @@
         <v>102</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>511</v>
@@ -8524,16 +8497,16 @@
         <v>102</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>511</v>
@@ -8583,16 +8556,16 @@
         <v>102</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>511</v>
@@ -8642,16 +8615,16 @@
         <v>102</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>511</v>
@@ -8701,16 +8674,16 @@
         <v>102</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>511</v>
@@ -8760,58 +8733,58 @@
         <v>102</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -8819,16 +8792,16 @@
         <v>102</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>521</v>
@@ -8875,238 +8848,238 @@
     </row>
     <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>252</v>
+        <v>744</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="H97" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>254</v>
+        <v>521</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" ht="45" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>522</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>628</v>
+        <v>745</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>130</v>
+        <v>745</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" ht="75" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>261</v>
+        <v>522</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>628</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="75" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>529</v>
+        <v>261</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9114,22 +9087,22 @@
         <v>249</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>526</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>629</v>
+        <v>506</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>506</v>
@@ -9168,122 +9141,122 @@
         <v>506</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="G102" s="8" t="s">
+      <c r="G102" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="H102" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="H102" s="8" t="s">
+      <c r="I102" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="J102" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>527</v>
-      </c>
       <c r="K102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="103" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="G103" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="H103" s="3" t="s">
+      <c r="H103" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="I103" s="4" t="s">
-        <v>529</v>
+      <c r="I103" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="Q103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="S103" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
     </row>
     <row r="104" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9291,16 +9264,16 @@
         <v>249</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>526</v>
@@ -9350,16 +9323,16 @@
         <v>249</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>526</v>
@@ -9404,21 +9377,21 @@
         <v>506</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>526</v>
@@ -9463,21 +9436,21 @@
         <v>506</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>526</v>
@@ -9527,16 +9500,16 @@
         <v>249</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>526</v>
@@ -9586,16 +9559,16 @@
         <v>249</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>526</v>
@@ -9645,16 +9618,16 @@
         <v>249</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>526</v>
@@ -9704,16 +9677,16 @@
         <v>249</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>526</v>
@@ -9727,35 +9700,35 @@
       <c r="I111" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="J111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="O111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R111" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S111" s="11" t="s">
-        <v>660</v>
+      <c r="J111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="K111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="L111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="M111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="N111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="O111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="P111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="R111" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="S111" s="3" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="112" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9763,16 +9736,16 @@
         <v>249</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>526</v>
@@ -9786,35 +9759,35 @@
       <c r="I112" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="J112" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="M112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="N112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="O112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="P112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="R112" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="S112" s="3" t="s">
-        <v>506</v>
+      <c r="J112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R112" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S112" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="113" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9822,176 +9795,176 @@
         <v>249</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="G113" s="8" t="s">
+      <c r="G113" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="H113" s="8" t="s">
+      <c r="H113" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="I113" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>527</v>
+      <c r="I113" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>506</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="P113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="Q113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="R113" s="3" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="S113" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19" ht="150" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>630</v>
+        <v>506</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="I114" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="J114" s="8" t="s">
-        <v>630</v>
+        <v>506</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>748</v>
+        <v>527</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>748</v>
+        <v>527</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>749</v>
+        <v>527</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>749</v>
+        <v>527</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>749</v>
+        <v>527</v>
       </c>
       <c r="P114" s="3" t="s">
-        <v>749</v>
+        <v>527</v>
       </c>
       <c r="Q114" s="3" t="s">
-        <v>749</v>
+        <v>527</v>
       </c>
       <c r="R114" s="3" t="s">
-        <v>749</v>
+        <v>527</v>
       </c>
       <c r="S114" s="3" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="115" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" ht="150" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="G115" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>130</v>
+      <c r="G115" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>630</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>130</v>
+        <v>748</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>130</v>
+        <v>748</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>130</v>
+        <v>749</v>
       </c>
       <c r="N115" s="3" t="s">
-        <v>130</v>
+        <v>749</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>130</v>
+        <v>749</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>130</v>
+        <v>749</v>
       </c>
       <c r="Q115" s="3" t="s">
-        <v>130</v>
+        <v>749</v>
       </c>
       <c r="R115" s="3" t="s">
-        <v>130</v>
+        <v>749</v>
       </c>
       <c r="S115" s="3" t="s">
-        <v>130</v>
+        <v>749</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -9999,16 +9972,16 @@
         <v>249</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>531</v>
@@ -10058,16 +10031,16 @@
         <v>249</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>531</v>
@@ -10117,16 +10090,16 @@
         <v>249</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>531</v>
@@ -10171,240 +10144,240 @@
         <v>130</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="R119" s="3" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="S119" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" ht="135" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="G120" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="H120" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="I120" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="J120" s="8" t="s">
-        <v>750</v>
+      <c r="G120" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="P120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="Q120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="R120" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="S120" s="3" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="135" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="G121" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="I121" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="J121" s="3" t="s">
-        <v>539</v>
+      <c r="G121" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="J121" s="8" t="s">
+        <v>750</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>539</v>
+        <v>751</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>539</v>
+        <v>751</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>539</v>
+        <v>751</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>539</v>
+        <v>751</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>539</v>
+        <v>751</v>
       </c>
       <c r="P121" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="Q121" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R121" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S121" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>751</v>
+      </c>
+      <c r="Q121" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="R121" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="S121" s="3" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="G122" s="3" t="s">
-        <v>541</v>
+      <c r="G122" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>541</v>
+        <v>631</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P122" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="Q122" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="R122" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="S122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
+      </c>
+      <c r="Q122" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R122" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S122" s="11" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="123" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -10412,292 +10385,294 @@
         <v>249</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="G123" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="H123" s="8" t="s">
-        <v>516</v>
+      <c r="G123" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>541</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="P123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="Q123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="R123" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="S123" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="124" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>322</v>
+        <v>535</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>516</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="P124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="Q124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="R124" s="3" t="s">
-        <v>322</v>
+        <v>527</v>
       </c>
       <c r="S124" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19" ht="135" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="G125" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="H125" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="I125" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="J125" s="8" t="s">
-        <v>750</v>
+      <c r="G125" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="P125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="Q125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="R125" s="3" t="s">
-        <v>751</v>
+        <v>322</v>
       </c>
       <c r="S125" s="3" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" ht="135" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>543</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>633</v>
+        <v>750</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>633</v>
+        <v>750</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="J126" s="3" t="s">
-        <v>635</v>
+        <v>750</v>
+      </c>
+      <c r="J126" s="8" t="s">
+        <v>750</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>635</v>
+        <v>751</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>546</v>
+        <v>751</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>546</v>
+        <v>751</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>546</v>
+        <v>751</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>546</v>
+        <v>751</v>
       </c>
       <c r="P126" s="3" t="s">
-        <v>546</v>
+        <v>751</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>546</v>
+        <v>751</v>
       </c>
       <c r="R126" s="3" t="s">
-        <v>546</v>
+        <v>751</v>
       </c>
       <c r="S126" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>755</v>
+        <v>341</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>756</v>
+        <v>342</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="F127" s="2"/>
-      <c r="G127" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H127" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I127" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="J127" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="K127" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="L127" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="M127" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="N127" s="11" t="s">
-        <v>660</v>
+        <v>343</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="K127" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="L127" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="M127" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="N127" s="3" t="s">
+        <v>546</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>758</v>
+        <v>546</v>
       </c>
       <c r="P127" s="3" t="s">
-        <v>759</v>
+        <v>546</v>
       </c>
       <c r="Q127" s="3" t="s">
-        <v>760</v>
+        <v>546</v>
       </c>
       <c r="R127" s="3" t="s">
-        <v>761</v>
+        <v>546</v>
       </c>
       <c r="S127" s="3" t="s">
-        <v>762</v>
+        <v>546</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.2">
@@ -10705,294 +10680,292 @@
         <v>249</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>344</v>
+        <v>755</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>345</v>
+        <v>756</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="I128" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="J128" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="K128" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="L128" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="M128" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="N128" s="3" t="s">
-        <v>549</v>
+        <v>757</v>
+      </c>
+      <c r="F128" s="2"/>
+      <c r="G128" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H128" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I128" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="J128" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="K128" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="L128" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="M128" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="N128" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>549</v>
+        <v>758</v>
       </c>
       <c r="P128" s="3" t="s">
-        <v>549</v>
+        <v>759</v>
       </c>
       <c r="Q128" s="3" t="s">
-        <v>549</v>
+        <v>760</v>
       </c>
       <c r="R128" s="3" t="s">
-        <v>549</v>
+        <v>761</v>
       </c>
       <c r="S128" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G129" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="H129" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="I129" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="J129" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="K129" s="4" t="s">
-        <v>550</v>
+      <c r="G129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="K129" s="3" t="s">
+        <v>549</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="O129" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="P129" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q129" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R129" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S129" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="130" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>549</v>
+      </c>
+      <c r="O129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="P129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="R129" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="S129" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="I130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="J130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="K130" s="3" t="s">
-        <v>353</v>
+      <c r="G130" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="J130" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K130" s="4" t="s">
+        <v>550</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>353</v>
+        <v>550</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>353</v>
+        <v>550</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="P130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="R130" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="S130" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="131" spans="1:19" ht="60" x14ac:dyDescent="0.2">
+        <v>550</v>
+      </c>
+      <c r="O130" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="P130" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q130" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R130" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S130" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G131" s="8" t="s">
-        <v>632</v>
+      <c r="G131" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="I131" s="4" t="s">
-        <v>632</v>
+        <v>353</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="P131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="Q131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="R131" s="3" t="s">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="S131" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G132" s="3" t="s">
-        <v>754</v>
+      <c r="G132" s="8" t="s">
+        <v>632</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="I132" s="3" t="s">
-        <v>754</v>
+        <v>631</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="P132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="Q132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="R132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
       <c r="S132" s="3" t="s">
-        <v>754</v>
+        <v>539</v>
       </c>
     </row>
     <row r="133" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -11000,353 +10973,353 @@
         <v>249</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G133" s="8" t="s">
-        <v>639</v>
+      <c r="G133" s="3" t="s">
+        <v>754</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="Q133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="R133" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="S133" s="3" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G134" s="3" t="s">
-        <v>130</v>
+      <c r="G134" s="8" t="s">
+        <v>639</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="P134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="Q134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="R134" s="3" t="s">
-        <v>130</v>
+        <v>753</v>
       </c>
       <c r="S134" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="135" spans="1:19" ht="90" x14ac:dyDescent="0.2">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>548</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="N135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="P135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="Q135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="R135" s="3" t="s">
-        <v>369</v>
+        <v>130</v>
       </c>
       <c r="S135" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" ht="90" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>556</v>
+        <v>369</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="P136" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q136" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="R136" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="S136" s="11" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="137" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+      <c r="P136" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q136" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="R136" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="S136" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N137" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="P137" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="Q137" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="R137" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="S137" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19" ht="150" x14ac:dyDescent="0.2">
+        <v>556</v>
+      </c>
+      <c r="P137" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q137" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="R137" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="S137" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="G138" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="H138" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="I138" s="8" t="s">
-        <v>640</v>
+      <c r="G138" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>557</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>641</v>
+        <v>557</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>642</v>
+        <v>557</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>643</v>
+        <v>557</v>
       </c>
       <c r="M138" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="P138" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q138" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R138" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="S138" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="139" spans="1:19" ht="150" x14ac:dyDescent="0.2">
@@ -11354,22 +11327,22 @@
         <v>249</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>640</v>
@@ -11378,7 +11351,7 @@
         <v>640</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K139" s="3" t="s">
         <v>642</v>
@@ -11413,31 +11386,31 @@
         <v>249</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G140" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="H140" s="8" t="s">
         <v>640</v>
-      </c>
-      <c r="H140" s="8" t="s">
-        <v>645</v>
       </c>
       <c r="I140" s="8" t="s">
         <v>640</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="K140" s="3" t="s">
         <v>642</v>
@@ -11472,25 +11445,25 @@
         <v>249</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="I141" s="8" t="s">
         <v>640</v>
@@ -11531,22 +11504,22 @@
         <v>249</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>640</v>
@@ -11590,16 +11563,16 @@
         <v>249</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>555</v>
@@ -11649,16 +11622,16 @@
         <v>249</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>555</v>
@@ -11708,22 +11681,22 @@
         <v>249</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>640</v>
@@ -11767,22 +11740,22 @@
         <v>249</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="H146" s="8" t="s">
         <v>640</v>
@@ -11826,16 +11799,16 @@
         <v>249</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>555</v>
@@ -11844,7 +11817,7 @@
         <v>640</v>
       </c>
       <c r="H147" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="I147" s="8" t="s">
         <v>640</v>
@@ -11885,25 +11858,25 @@
         <v>249</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="H148" s="8" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="I148" s="8" t="s">
         <v>640</v>
@@ -11944,22 +11917,22 @@
         <v>249</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>555</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="H149" s="8" t="s">
         <v>640</v>
@@ -11998,63 +11971,63 @@
         <v>558</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19" ht="150" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="G150" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H150" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="I150" s="11" t="s">
-        <v>660</v>
+        <v>555</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="H150" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="I150" s="8" t="s">
+        <v>640</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>224</v>
+        <v>646</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>224</v>
+        <v>642</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>224</v>
+        <v>643</v>
       </c>
       <c r="M150" s="3" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
       <c r="N150" s="3" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
       <c r="O150" s="3" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
       <c r="P150" s="3" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
       <c r="Q150" s="3" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
       <c r="R150" s="3" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
       <c r="S150" s="3" t="s">
-        <v>224</v>
+        <v>558</v>
       </c>
     </row>
     <row r="151" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -12062,58 +12035,58 @@
         <v>249</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="H151" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="I151" s="8" t="s">
-        <v>648</v>
+        <v>567</v>
+      </c>
+      <c r="G151" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="I151" s="11" t="s">
+        <v>660</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="M151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="N151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="O151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="P151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="Q151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="R151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="S151" s="3" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
     </row>
     <row r="152" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -12121,58 +12094,58 @@
         <v>249</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H152" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I152" s="3" t="s">
-        <v>130</v>
+      <c r="G152" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="I152" s="8" t="s">
+        <v>648</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="K152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="M152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="N152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="P152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="Q152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="R152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="S152" s="3" t="s">
-        <v>130</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -12180,65 +12153,124 @@
         <v>249</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>765</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>568</v>
       </c>
       <c r="G153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R153" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S153" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+      <c r="A154" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="G154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="H153" s="3" t="s">
+      <c r="H154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I153" s="3" t="s">
+      <c r="I154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="J153" s="3" t="s">
+      <c r="J154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="K153" s="3" t="s">
+      <c r="K154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="L153" s="3" t="s">
+      <c r="L154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="M153" s="3" t="s">
+      <c r="M154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="N153" s="3" t="s">
+      <c r="N154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="O153" s="3" t="s">
+      <c r="O154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="P153" s="3" t="s">
+      <c r="P154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="Q153" s="3" t="s">
+      <c r="Q154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="R153" s="3" t="s">
+      <c r="R154" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="S153" s="3" t="s">
+      <c r="S154" s="3" t="s">
         <v>425</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <mergeCells count="2">
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B64:B65"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
